--- a/distribucion.xlsx
+++ b/distribucion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Registro_defectos_SEHO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9AD0F3-D631-49AD-BA8A-70CB2DD538E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB55737-5B43-410C-B14B-52C55ADE5869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="6" xr2:uid="{C5A581BF-84BA-4755-84C9-6391AAA71289}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{C5A581BF-84BA-4755-84C9-6391AAA71289}"/>
   </bookViews>
   <sheets>
     <sheet name="Frame0" sheetId="2" r:id="rId1"/>
@@ -46,9 +46,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -87,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="614">
   <si>
     <t>FA08</t>
   </si>
@@ -1837,6 +1834,111 @@
   <si>
     <t>%TopDefecto</t>
   </si>
+  <si>
+    <t>Disponible_5:</t>
+  </si>
+  <si>
+    <t>Disponible_6:</t>
+  </si>
+  <si>
+    <t>Disponible_7:</t>
+  </si>
+  <si>
+    <t>Disponible_8:</t>
+  </si>
+  <si>
+    <t>Disponible_9:</t>
+  </si>
+  <si>
+    <t>label_181</t>
+  </si>
+  <si>
+    <t>label_182</t>
+  </si>
+  <si>
+    <t>entry_31</t>
+  </si>
+  <si>
+    <t>label_183</t>
+  </si>
+  <si>
+    <t>entry_32</t>
+  </si>
+  <si>
+    <t>label_184</t>
+  </si>
+  <si>
+    <t>entry_33</t>
+  </si>
+  <si>
+    <t>label_185</t>
+  </si>
+  <si>
+    <t>entry_34</t>
+  </si>
+  <si>
+    <t>entry_35</t>
+  </si>
+  <si>
+    <t>Row_31</t>
+  </si>
+  <si>
+    <t>Defecto 31</t>
+  </si>
+  <si>
+    <t>Row_32</t>
+  </si>
+  <si>
+    <t>Defecto 32</t>
+  </si>
+  <si>
+    <t>Row_33</t>
+  </si>
+  <si>
+    <t>Defecto 33</t>
+  </si>
+  <si>
+    <t>Row_34</t>
+  </si>
+  <si>
+    <t>Defecto 34</t>
+  </si>
+  <si>
+    <t>Row_35</t>
+  </si>
+  <si>
+    <t>Defecto 35</t>
+  </si>
+  <si>
+    <t>label_rd_88</t>
+  </si>
+  <si>
+    <t>label_rd_89</t>
+  </si>
+  <si>
+    <t>label_rd_90</t>
+  </si>
+  <si>
+    <t>label_rd_91</t>
+  </si>
+  <si>
+    <t>label_rd_92</t>
+  </si>
+  <si>
+    <t>label_rd_93</t>
+  </si>
+  <si>
+    <t>label_rd_94</t>
+  </si>
+  <si>
+    <t>label_rd_95</t>
+  </si>
+  <si>
+    <t>label_rd_96</t>
+  </si>
+  <si>
+    <t>label_rd_97</t>
+  </si>
 </sst>
 </file>
 
@@ -1985,7 +2087,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2133,6 +2235,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF4FD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2405,7 +2513,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2574,6 +2682,20 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2607,10 +2729,31 @@
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2618,6 +2761,15 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="23" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2631,88 +2783,33 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="38">
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2801,25 +2898,6 @@
         <bottom/>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -2922,6 +3000,24 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
         <vertical style="thin">
           <color indexed="64"/>
         </vertical>
@@ -2980,13 +3076,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3000,6 +3089,32 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -3599,9 +3714,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFDFF4FD"/>
       <color rgb="FFD9D9D9"/>
       <color rgb="FFFFFFC9"/>
-      <color rgb="FFDFF4FD"/>
       <color rgb="FFF2CEEF"/>
       <color rgb="FF83E28E"/>
       <color rgb="FFFF3737"/>
@@ -67779,16 +67894,16 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{807C3920-3E36-4FED-A44E-343976B18993}" name="Tabla1" displayName="Tabla1" ref="K10:R14" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="18" tableBorderDxfId="19" totalsRowBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{807C3920-3E36-4FED-A44E-343976B18993}" name="Tabla1" displayName="Tabla1" ref="K10:R14" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{1CDBF142-46B8-4539-A026-F389B4154794}" name="Pallets" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{C16B6F37-CBB3-4AD9-BA6D-75E07FAD3622}" name="V/SEHO" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{D65E6DFA-D408-404D-9C63-C1F754CBE96B}" name="Defectos" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{9A0E38CC-BB39-4458-B4D2-C733B3D682E2}" name="Producido" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{7DFC2CF1-E71B-4EBE-A54D-7366C9A2A878}" name="FPY" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{DC225E35-BE7A-4CA4-B9D7-8B6A7E490178}" name="TopDefecto" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{82511484-AD69-4EE7-95B9-170355C8DF18}" name="C/TopDefecto" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{6EB317C6-5621-4DB1-888A-ADE2A599E63E}" name="%TopDefecto" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{1CDBF142-46B8-4539-A026-F389B4154794}" name="Pallets" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{C16B6F37-CBB3-4AD9-BA6D-75E07FAD3622}" name="V/SEHO" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{D65E6DFA-D408-404D-9C63-C1F754CBE96B}" name="Defectos" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{9A0E38CC-BB39-4458-B4D2-C733B3D682E2}" name="Producido" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{7DFC2CF1-E71B-4EBE-A54D-7366C9A2A878}" name="FPY" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{DC225E35-BE7A-4CA4-B9D7-8B6A7E490178}" name="TopDefecto" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{82511484-AD69-4EE7-95B9-170355C8DF18}" name="C/TopDefecto" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{6EB317C6-5621-4DB1-888A-ADE2A599E63E}" name="%TopDefecto" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -68196,26 +68311,26 @@
       <c r="A1" s="5" t="s">
         <v>545</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="95" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="77" t="s">
+      <c r="C1" s="96"/>
+      <c r="D1" s="95" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="78"/>
+      <c r="E1" s="96"/>
       <c r="F1" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="77" t="s">
+      <c r="G1" s="95" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="84"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="77" t="s">
+      <c r="H1" s="97"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="K1" s="78"/>
+      <c r="K1" s="96"/>
       <c r="L1" s="59" t="s">
         <v>48</v>
       </c>
@@ -68224,42 +68339,42 @@
       <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="88" t="s">
         <v>182</v>
       </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
     </row>
     <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="79" t="s">
         <v>480</v>
       </c>
-      <c r="C3" s="82"/>
-      <c r="D3" s="83" t="s">
+      <c r="C3" s="79"/>
+      <c r="D3" s="80" t="s">
         <v>555</v>
       </c>
-      <c r="E3" s="83"/>
+      <c r="E3" s="80"/>
       <c r="F3" s="54"/>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="90" t="s">
         <v>481</v>
       </c>
-      <c r="H3" s="80"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="75" t="s">
+      <c r="H3" s="91"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="93" t="s">
         <v>439</v>
       </c>
-      <c r="K3" s="76"/>
+      <c r="K3" s="94"/>
       <c r="L3" s="55" t="s">
         <v>482</v>
       </c>
@@ -68268,86 +68383,86 @@
       <c r="A4" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="79" t="s">
         <v>441</v>
       </c>
-      <c r="C4" s="82"/>
-      <c r="D4" s="83" t="e">
+      <c r="C4" s="79"/>
+      <c r="D4" s="80" t="e">
         <f>SUMIFS([1]Register_global!$D:$D,[1]Register_global!$A:$A,[1]Defectos!$I$9,[1]Register_global!$E:$E,[1]Defectos!$E$5,[1]Register_global!$AO:$AO,"&gt;="&amp;TEXT([1]Defectos!$G$5*24,"0"),[1]Register_global!$AO:$AO,"&lt;"&amp;TEXT([1]Defectos!$H$5*24,"0"))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E4" s="83"/>
+      <c r="E4" s="80"/>
       <c r="F4" s="56">
         <v>1</v>
       </c>
-      <c r="G4" s="90" t="e">
+      <c r="G4" s="81" t="e">
         <f>_xlfn.XLOOKUP(J4,$A$2:$A$6,#REF!,"N/A",0)</f>
         <v>#NUM!</v>
       </c>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="91" t="e">
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82" t="e">
         <f>LARGE($A$2:$A$6,1)</f>
         <v>#NUM!</v>
       </c>
-      <c r="K4" s="91"/>
+      <c r="K4" s="82"/>
       <c r="L4" s="57" t="str">
         <f>IFERROR(((J4*100)/#REF!),"N/A")</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="99" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="82" t="s">
+      <c r="B5" s="79" t="s">
         <v>440</v>
       </c>
-      <c r="C5" s="82"/>
-      <c r="D5" s="87" t="str">
+      <c r="C5" s="79"/>
+      <c r="D5" s="98" t="str">
         <f>IFERROR(100-((#REF!*100)/#REF!),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="E5" s="87"/>
+      <c r="E5" s="98"/>
       <c r="F5" s="56">
         <v>2</v>
       </c>
-      <c r="G5" s="85" t="e">
+      <c r="G5" s="84" t="e">
         <f>_xlfn.XLOOKUP(J5,$A$2:$A$6,#REF!,"N/A",0)</f>
         <v>#NUM!</v>
       </c>
-      <c r="H5" s="86"/>
-      <c r="I5" s="86"/>
-      <c r="J5" s="86" t="e">
+      <c r="H5" s="85"/>
+      <c r="I5" s="85"/>
+      <c r="J5" s="85" t="e">
         <f>LARGE($A$2:$A$6,2)</f>
         <v>#NUM!</v>
       </c>
-      <c r="K5" s="86"/>
+      <c r="K5" s="85"/>
       <c r="L5" s="57" t="str">
         <f>IFERROR(((J5*100)/#REF!),"N/A")</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="72"/>
-      <c r="B6" s="82"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="87"/>
-      <c r="E6" s="87"/>
+      <c r="A6" s="100"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="98"/>
+      <c r="E6" s="98"/>
       <c r="F6" s="56">
         <v>3</v>
       </c>
-      <c r="G6" s="88" t="e">
+      <c r="G6" s="86" t="e">
         <f>_xlfn.XLOOKUP(J6,$A$2:$A$6,#REF!,"N/A",0)</f>
         <v>#NUM!</v>
       </c>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="89" t="e">
+      <c r="H6" s="87"/>
+      <c r="I6" s="87"/>
+      <c r="J6" s="87" t="e">
         <f>LARGE($A$2:$A$6,3)</f>
         <v>#NUM!</v>
       </c>
-      <c r="K6" s="89"/>
+      <c r="K6" s="87"/>
       <c r="L6" s="58" t="str">
         <f>IFERROR(((J6*100)/#REF!),"N/A")</f>
         <v>N/A</v>
@@ -68357,26 +68472,26 @@
       <c r="A9" s="5" t="s">
         <v>545</v>
       </c>
-      <c r="B9" s="77" t="s">
+      <c r="B9" s="95" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="78"/>
-      <c r="D9" s="77" t="s">
+      <c r="C9" s="96"/>
+      <c r="D9" s="95" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="78"/>
+      <c r="E9" s="96"/>
       <c r="F9" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="77" t="s">
+      <c r="G9" s="95" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="84"/>
-      <c r="I9" s="78"/>
-      <c r="J9" s="77" t="s">
+      <c r="H9" s="97"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="K9" s="78"/>
+      <c r="K9" s="96"/>
       <c r="L9" s="59" t="s">
         <v>48</v>
       </c>
@@ -68385,42 +68500,42 @@
       <c r="A10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="73" t="s">
+      <c r="B10" s="88" t="s">
         <v>551</v>
       </c>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="74"/>
-      <c r="K10" s="74"/>
-      <c r="L10" s="74"/>
+      <c r="C10" s="89"/>
+      <c r="D10" s="89"/>
+      <c r="E10" s="89"/>
+      <c r="F10" s="89"/>
+      <c r="G10" s="89"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="89"/>
+      <c r="J10" s="89"/>
+      <c r="K10" s="89"/>
+      <c r="L10" s="89"/>
     </row>
     <row r="11" spans="1:12" ht="18" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="82" t="s">
+      <c r="B11" s="79" t="s">
         <v>552</v>
       </c>
-      <c r="C11" s="82"/>
-      <c r="D11" s="83" t="s">
+      <c r="C11" s="79"/>
+      <c r="D11" s="80" t="s">
         <v>553</v>
       </c>
-      <c r="E11" s="83"/>
+      <c r="E11" s="80"/>
       <c r="F11" s="54"/>
-      <c r="G11" s="79" t="s">
+      <c r="G11" s="90" t="s">
         <v>554</v>
       </c>
-      <c r="H11" s="80"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="75" t="s">
+      <c r="H11" s="91"/>
+      <c r="I11" s="92"/>
+      <c r="J11" s="93" t="s">
         <v>556</v>
       </c>
-      <c r="K11" s="76"/>
+      <c r="K11" s="94"/>
       <c r="L11" s="55" t="s">
         <v>557</v>
       </c>
@@ -68429,26 +68544,26 @@
       <c r="A12" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="82" t="s">
+      <c r="B12" s="79" t="s">
         <v>558</v>
       </c>
-      <c r="C12" s="82"/>
-      <c r="D12" s="83" t="s">
+      <c r="C12" s="79"/>
+      <c r="D12" s="80" t="s">
         <v>559</v>
       </c>
-      <c r="E12" s="83"/>
+      <c r="E12" s="80"/>
       <c r="F12" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="G12" s="90" t="s">
+      <c r="G12" s="81" t="s">
         <v>561</v>
       </c>
-      <c r="H12" s="91"/>
-      <c r="I12" s="91"/>
-      <c r="J12" s="91" t="s">
+      <c r="H12" s="82"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="82" t="s">
         <v>562</v>
       </c>
-      <c r="K12" s="91"/>
+      <c r="K12" s="82"/>
       <c r="L12" s="57" t="s">
         <v>563</v>
       </c>
@@ -68457,26 +68572,26 @@
       <c r="A13" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="82" t="s">
+      <c r="B13" s="79" t="s">
         <v>564</v>
       </c>
-      <c r="C13" s="82"/>
-      <c r="D13" s="92" t="s">
+      <c r="C13" s="79"/>
+      <c r="D13" s="83" t="s">
         <v>565</v>
       </c>
-      <c r="E13" s="92"/>
+      <c r="E13" s="83"/>
       <c r="F13" s="56" t="s">
         <v>566</v>
       </c>
-      <c r="G13" s="85" t="s">
+      <c r="G13" s="84" t="s">
         <v>567</v>
       </c>
-      <c r="H13" s="86"/>
-      <c r="I13" s="86"/>
-      <c r="J13" s="86" t="s">
+      <c r="H13" s="85"/>
+      <c r="I13" s="85"/>
+      <c r="J13" s="85" t="s">
         <v>568</v>
       </c>
-      <c r="K13" s="86"/>
+      <c r="K13" s="85"/>
       <c r="L13" s="57" t="s">
         <v>569</v>
       </c>
@@ -68485,43 +68600,38 @@
       <c r="A14" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="82"/>
-      <c r="C14" s="82"/>
-      <c r="D14" s="92"/>
-      <c r="E14" s="92"/>
+      <c r="B14" s="79"/>
+      <c r="C14" s="79"/>
+      <c r="D14" s="83"/>
+      <c r="E14" s="83"/>
       <c r="F14" s="56" t="s">
         <v>570</v>
       </c>
-      <c r="G14" s="88" t="s">
+      <c r="G14" s="86" t="s">
         <v>571</v>
       </c>
-      <c r="H14" s="89"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="89" t="s">
+      <c r="H14" s="87"/>
+      <c r="I14" s="87"/>
+      <c r="J14" s="87" t="s">
         <v>572</v>
       </c>
-      <c r="K14" s="89"/>
+      <c r="K14" s="87"/>
       <c r="L14" s="58" t="s">
         <v>573</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="B13:C14"/>
-    <mergeCell ref="D13:E14"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="B10:L10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="B1:C1"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="G9:I9"/>
@@ -68536,43 +68646,48 @@
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="J4:K4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B10:L10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="B13:C14"/>
+    <mergeCell ref="D13:E14"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:K14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="D5">
-    <cfRule type="cellIs" dxfId="8" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="15" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="16" operator="equal">
       <formula>86.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="17" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="17" operator="lessThan">
       <formula>86.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="18" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="18" operator="greaterThan">
       <formula>86.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>86.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="lessThan">
       <formula>86.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThan">
       <formula>86.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68781,14 +68896,14 @@
         <v>41</v>
       </c>
       <c r="B2" s="14"/>
-      <c r="C2" s="93" t="s">
+      <c r="C2" s="101" t="s">
         <v>404</v>
       </c>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
       <c r="I2" s="17"/>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68902,14 +69017,14 @@
         <v>41</v>
       </c>
       <c r="B9" s="14"/>
-      <c r="C9" s="93" t="s">
+      <c r="C9" s="101" t="s">
         <v>387</v>
       </c>
-      <c r="D9" s="93"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="93"/>
-      <c r="G9" s="93"/>
-      <c r="H9" s="93"/>
+      <c r="D9" s="101"/>
+      <c r="E9" s="101"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="101"/>
+      <c r="H9" s="101"/>
       <c r="I9" s="17"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -69061,7 +69176,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D077AAEA-2C62-4252-81FA-F27EE73ED170}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="37.28515625" customWidth="1"/>
@@ -69115,18 +69230,18 @@
       <c r="A2" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
     </row>
     <row r="3" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A3" s="9" t="s">
@@ -69282,18 +69397,26 @@
       <c r="A9" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="62"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="E9" s="11"/>
+      <c r="F9" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="K9" s="11"/>
     </row>
     <row r="10" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A10" s="9" t="s">
@@ -69302,321 +69425,373 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
+      <c r="E10" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+    <row r="11" spans="1:11" ht="24" x14ac:dyDescent="0.4">
+      <c r="A11" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B14" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I14" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J14" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K14" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+    <row r="15" spans="1:11" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="61" t="s">
+      <c r="B15" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="61"/>
-    </row>
-    <row r="15" spans="1:11" ht="24" x14ac:dyDescent="0.4">
-      <c r="A15" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="K15" s="11" t="s">
-        <v>75</v>
-      </c>
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="69"/>
     </row>
     <row r="16" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A16" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A17" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A18" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A19" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A20" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>164</v>
+        <v>104</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>165</v>
+        <v>106</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>166</v>
+        <v>108</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>167</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A21" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="62" t="s">
-        <v>130</v>
-      </c>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="22" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A22" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>590</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>592</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="24" x14ac:dyDescent="0.4">
+      <c r="A23" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="60" t="s">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="70" t="s">
+        <v>130</v>
+      </c>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+    </row>
+    <row r="24" spans="1:11" ht="24" x14ac:dyDescent="0.4">
+      <c r="A24" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E23" s="16"/>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E25" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E24:H24"/>
     <mergeCell ref="B2:K2"/>
-    <mergeCell ref="E9:H9"/>
     <mergeCell ref="E10:H10"/>
-    <mergeCell ref="B14:K14"/>
-    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="B15:K15"/>
+    <mergeCell ref="E23:H23"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -71399,47 +71574,47 @@
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E9" s="65" t="s">
+      <c r="E9" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65" t="s">
+      <c r="F9" s="73"/>
+      <c r="G9" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="65"/>
+      <c r="H9" s="73"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D10" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="66" t="s">
+      <c r="E10" s="74" t="s">
         <v>546</v>
       </c>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="K10" s="95" t="s">
+      <c r="F10" s="74"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="74"/>
+      <c r="K10" s="61" t="s">
         <v>574</v>
       </c>
-      <c r="L10" s="96" t="s">
+      <c r="L10" s="62" t="s">
         <v>575</v>
       </c>
-      <c r="M10" s="96" t="s">
+      <c r="M10" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="N10" s="96" t="s">
+      <c r="N10" s="62" t="s">
         <v>441</v>
       </c>
-      <c r="O10" s="96" t="s">
+      <c r="O10" s="62" t="s">
         <v>440</v>
       </c>
-      <c r="P10" s="96" t="s">
+      <c r="P10" s="62" t="s">
         <v>577</v>
       </c>
-      <c r="Q10" s="96" t="s">
+      <c r="Q10" s="62" t="s">
         <v>576</v>
       </c>
-      <c r="R10" s="97" t="s">
+      <c r="R10" s="63" t="s">
         <v>578</v>
       </c>
     </row>
@@ -71447,110 +71622,110 @@
       <c r="D11" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="67" t="s">
+      <c r="E11" s="75" t="s">
         <v>547</v>
       </c>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="K11" s="98"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="K11" s="64"/>
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" s="17"/>
       <c r="O11" s="17"/>
       <c r="P11" s="17"/>
       <c r="Q11" s="17"/>
-      <c r="R11" s="99"/>
+      <c r="R11" s="65"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D12" s="63" t="s">
+      <c r="D12" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="68" t="s">
+      <c r="E12" s="76" t="s">
         <v>548</v>
       </c>
-      <c r="F12" s="68"/>
-      <c r="G12" s="69" t="s">
+      <c r="F12" s="76"/>
+      <c r="G12" s="77" t="s">
         <v>549</v>
       </c>
-      <c r="H12" s="69"/>
-      <c r="K12" s="100"/>
-      <c r="L12" s="101"/>
-      <c r="M12" s="101"/>
-      <c r="N12" s="101"/>
-      <c r="O12" s="101"/>
-      <c r="P12" s="101"/>
-      <c r="Q12" s="101"/>
-      <c r="R12" s="94"/>
+      <c r="H12" s="77"/>
+      <c r="K12" s="66"/>
+      <c r="L12" s="67"/>
+      <c r="M12" s="67"/>
+      <c r="N12" s="67"/>
+      <c r="O12" s="67"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="60"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D13" s="64"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="K13" s="98"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="K13" s="64"/>
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" s="17"/>
       <c r="O13" s="17"/>
       <c r="P13" s="17"/>
       <c r="Q13" s="17"/>
-      <c r="R13" s="99"/>
+      <c r="R13" s="65"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D14" s="64"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
-      <c r="K14" s="100"/>
-      <c r="L14" s="101"/>
-      <c r="M14" s="101"/>
-      <c r="N14" s="101"/>
-      <c r="O14" s="101"/>
-      <c r="P14" s="101"/>
-      <c r="Q14" s="101"/>
-      <c r="R14" s="94"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="67"/>
+      <c r="M14" s="67"/>
+      <c r="N14" s="67"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="67"/>
+      <c r="Q14" s="67"/>
+      <c r="R14" s="60"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D15" s="64"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="69"/>
-      <c r="H15" s="69"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D16" s="63" t="s">
+      <c r="D16" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="68"/>
-      <c r="F16" s="68"/>
-      <c r="G16" s="70" t="s">
+      <c r="E16" s="76"/>
+      <c r="F16" s="76"/>
+      <c r="G16" s="78" t="s">
         <v>550</v>
       </c>
-      <c r="H16" s="70"/>
+      <c r="H16" s="78"/>
     </row>
     <row r="17" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D17" s="64"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="68"/>
-      <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="76"/>
+      <c r="F17" s="76"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="78"/>
     </row>
     <row r="18" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D18" s="64"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="70"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="78"/>
     </row>
     <row r="19" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D19" s="64"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="76"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -71752,7 +71927,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E87CC77D-451D-4938-839F-1695B8C726C1}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -72333,6 +72508,96 @@
       </c>
       <c r="H32" s="3" t="s">
         <v>544</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" s="104" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="102" t="s">
+        <v>594</v>
+      </c>
+      <c r="B33" s="102" t="s">
+        <v>595</v>
+      </c>
+      <c r="C33" s="103"/>
+      <c r="F33" s="102" t="s">
+        <v>594</v>
+      </c>
+      <c r="G33" s="102" t="s">
+        <v>604</v>
+      </c>
+      <c r="H33" s="103" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>597</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="F34" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="H34" s="103" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>599</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="F35" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="H35" s="103" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>601</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="F36" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>607</v>
+      </c>
+      <c r="H36" s="103" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>603</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="F37" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="H37" s="103" t="s">
+        <v>613</v>
       </c>
     </row>
   </sheetData>

--- a/distribucion.xlsx
+++ b/distribucion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Registro_defectos_SEHO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB55737-5B43-410C-B14B-52C55ADE5869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9AD0F3-D631-49AD-BA8A-70CB2DD538E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{C5A581BF-84BA-4755-84C9-6391AAA71289}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="6" xr2:uid="{C5A581BF-84BA-4755-84C9-6391AAA71289}"/>
   </bookViews>
   <sheets>
     <sheet name="Frame0" sheetId="2" r:id="rId1"/>
@@ -46,6 +46,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -84,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="579">
   <si>
     <t>FA08</t>
   </si>
@@ -1834,111 +1837,6 @@
   <si>
     <t>%TopDefecto</t>
   </si>
-  <si>
-    <t>Disponible_5:</t>
-  </si>
-  <si>
-    <t>Disponible_6:</t>
-  </si>
-  <si>
-    <t>Disponible_7:</t>
-  </si>
-  <si>
-    <t>Disponible_8:</t>
-  </si>
-  <si>
-    <t>Disponible_9:</t>
-  </si>
-  <si>
-    <t>label_181</t>
-  </si>
-  <si>
-    <t>label_182</t>
-  </si>
-  <si>
-    <t>entry_31</t>
-  </si>
-  <si>
-    <t>label_183</t>
-  </si>
-  <si>
-    <t>entry_32</t>
-  </si>
-  <si>
-    <t>label_184</t>
-  </si>
-  <si>
-    <t>entry_33</t>
-  </si>
-  <si>
-    <t>label_185</t>
-  </si>
-  <si>
-    <t>entry_34</t>
-  </si>
-  <si>
-    <t>entry_35</t>
-  </si>
-  <si>
-    <t>Row_31</t>
-  </si>
-  <si>
-    <t>Defecto 31</t>
-  </si>
-  <si>
-    <t>Row_32</t>
-  </si>
-  <si>
-    <t>Defecto 32</t>
-  </si>
-  <si>
-    <t>Row_33</t>
-  </si>
-  <si>
-    <t>Defecto 33</t>
-  </si>
-  <si>
-    <t>Row_34</t>
-  </si>
-  <si>
-    <t>Defecto 34</t>
-  </si>
-  <si>
-    <t>Row_35</t>
-  </si>
-  <si>
-    <t>Defecto 35</t>
-  </si>
-  <si>
-    <t>label_rd_88</t>
-  </si>
-  <si>
-    <t>label_rd_89</t>
-  </si>
-  <si>
-    <t>label_rd_90</t>
-  </si>
-  <si>
-    <t>label_rd_91</t>
-  </si>
-  <si>
-    <t>label_rd_92</t>
-  </si>
-  <si>
-    <t>label_rd_93</t>
-  </si>
-  <si>
-    <t>label_rd_94</t>
-  </si>
-  <si>
-    <t>label_rd_95</t>
-  </si>
-  <si>
-    <t>label_rd_96</t>
-  </si>
-  <si>
-    <t>label_rd_97</t>
-  </si>
 </sst>
 </file>
 
@@ -2087,7 +1985,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="27">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2235,12 +2133,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF4FD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2513,7 +2405,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2682,20 +2574,6 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2729,31 +2607,10 @@
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2761,15 +2618,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="23" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2783,33 +2631,88 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="38">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2898,6 +2801,25 @@
         <bottom/>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -3000,24 +2922,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
         <vertical style="thin">
           <color indexed="64"/>
         </vertical>
@@ -3076,6 +2980,13 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3089,32 +3000,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -3714,9 +3599,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFDFF4FD"/>
       <color rgb="FFD9D9D9"/>
       <color rgb="FFFFFFC9"/>
+      <color rgb="FFDFF4FD"/>
       <color rgb="FFF2CEEF"/>
       <color rgb="FF83E28E"/>
       <color rgb="FFFF3737"/>
@@ -67894,16 +67779,16 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{807C3920-3E36-4FED-A44E-343976B18993}" name="Tabla1" displayName="Tabla1" ref="K10:R14" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{807C3920-3E36-4FED-A44E-343976B18993}" name="Tabla1" displayName="Tabla1" ref="K10:R14" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="18" tableBorderDxfId="19" totalsRowBorderDxfId="17">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{1CDBF142-46B8-4539-A026-F389B4154794}" name="Pallets" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{C16B6F37-CBB3-4AD9-BA6D-75E07FAD3622}" name="V/SEHO" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{D65E6DFA-D408-404D-9C63-C1F754CBE96B}" name="Defectos" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{9A0E38CC-BB39-4458-B4D2-C733B3D682E2}" name="Producido" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{7DFC2CF1-E71B-4EBE-A54D-7366C9A2A878}" name="FPY" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{DC225E35-BE7A-4CA4-B9D7-8B6A7E490178}" name="TopDefecto" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{82511484-AD69-4EE7-95B9-170355C8DF18}" name="C/TopDefecto" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{6EB317C6-5621-4DB1-888A-ADE2A599E63E}" name="%TopDefecto" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{1CDBF142-46B8-4539-A026-F389B4154794}" name="Pallets" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{C16B6F37-CBB3-4AD9-BA6D-75E07FAD3622}" name="V/SEHO" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{D65E6DFA-D408-404D-9C63-C1F754CBE96B}" name="Defectos" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{9A0E38CC-BB39-4458-B4D2-C733B3D682E2}" name="Producido" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{7DFC2CF1-E71B-4EBE-A54D-7366C9A2A878}" name="FPY" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{DC225E35-BE7A-4CA4-B9D7-8B6A7E490178}" name="TopDefecto" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{82511484-AD69-4EE7-95B9-170355C8DF18}" name="C/TopDefecto" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{6EB317C6-5621-4DB1-888A-ADE2A599E63E}" name="%TopDefecto" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -68311,26 +68196,26 @@
       <c r="A1" s="5" t="s">
         <v>545</v>
       </c>
-      <c r="B1" s="95" t="s">
+      <c r="B1" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="96"/>
-      <c r="D1" s="95" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="77" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="96"/>
+      <c r="E1" s="78"/>
       <c r="F1" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="95" t="s">
+      <c r="G1" s="77" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="97"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="95" t="s">
+      <c r="H1" s="84"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="77" t="s">
         <v>47</v>
       </c>
-      <c r="K1" s="96"/>
+      <c r="K1" s="78"/>
       <c r="L1" s="59" t="s">
         <v>48</v>
       </c>
@@ -68339,42 +68224,42 @@
       <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
     </row>
     <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="82" t="s">
         <v>480</v>
       </c>
-      <c r="C3" s="79"/>
-      <c r="D3" s="80" t="s">
+      <c r="C3" s="82"/>
+      <c r="D3" s="83" t="s">
         <v>555</v>
       </c>
-      <c r="E3" s="80"/>
+      <c r="E3" s="83"/>
       <c r="F3" s="54"/>
-      <c r="G3" s="90" t="s">
+      <c r="G3" s="79" t="s">
         <v>481</v>
       </c>
-      <c r="H3" s="91"/>
-      <c r="I3" s="92"/>
-      <c r="J3" s="93" t="s">
+      <c r="H3" s="80"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="75" t="s">
         <v>439</v>
       </c>
-      <c r="K3" s="94"/>
+      <c r="K3" s="76"/>
       <c r="L3" s="55" t="s">
         <v>482</v>
       </c>
@@ -68383,86 +68268,86 @@
       <c r="A4" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="82" t="s">
         <v>441</v>
       </c>
-      <c r="C4" s="79"/>
-      <c r="D4" s="80" t="e">
+      <c r="C4" s="82"/>
+      <c r="D4" s="83" t="e">
         <f>SUMIFS([1]Register_global!$D:$D,[1]Register_global!$A:$A,[1]Defectos!$I$9,[1]Register_global!$E:$E,[1]Defectos!$E$5,[1]Register_global!$AO:$AO,"&gt;="&amp;TEXT([1]Defectos!$G$5*24,"0"),[1]Register_global!$AO:$AO,"&lt;"&amp;TEXT([1]Defectos!$H$5*24,"0"))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E4" s="80"/>
+      <c r="E4" s="83"/>
       <c r="F4" s="56">
         <v>1</v>
       </c>
-      <c r="G4" s="81" t="e">
+      <c r="G4" s="90" t="e">
         <f>_xlfn.XLOOKUP(J4,$A$2:$A$6,#REF!,"N/A",0)</f>
         <v>#NUM!</v>
       </c>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82" t="e">
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="91" t="e">
         <f>LARGE($A$2:$A$6,1)</f>
         <v>#NUM!</v>
       </c>
-      <c r="K4" s="82"/>
+      <c r="K4" s="91"/>
       <c r="L4" s="57" t="str">
         <f>IFERROR(((J4*100)/#REF!),"N/A")</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="99" t="s">
+      <c r="A5" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="79" t="s">
+      <c r="B5" s="82" t="s">
         <v>440</v>
       </c>
-      <c r="C5" s="79"/>
-      <c r="D5" s="98" t="str">
+      <c r="C5" s="82"/>
+      <c r="D5" s="87" t="str">
         <f>IFERROR(100-((#REF!*100)/#REF!),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="E5" s="98"/>
+      <c r="E5" s="87"/>
       <c r="F5" s="56">
         <v>2</v>
       </c>
-      <c r="G5" s="84" t="e">
+      <c r="G5" s="85" t="e">
         <f>_xlfn.XLOOKUP(J5,$A$2:$A$6,#REF!,"N/A",0)</f>
         <v>#NUM!</v>
       </c>
-      <c r="H5" s="85"/>
-      <c r="I5" s="85"/>
-      <c r="J5" s="85" t="e">
+      <c r="H5" s="86"/>
+      <c r="I5" s="86"/>
+      <c r="J5" s="86" t="e">
         <f>LARGE($A$2:$A$6,2)</f>
         <v>#NUM!</v>
       </c>
-      <c r="K5" s="85"/>
+      <c r="K5" s="86"/>
       <c r="L5" s="57" t="str">
         <f>IFERROR(((J5*100)/#REF!),"N/A")</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="100"/>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="98"/>
-      <c r="E6" s="98"/>
+      <c r="A6" s="72"/>
+      <c r="B6" s="82"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
       <c r="F6" s="56">
         <v>3</v>
       </c>
-      <c r="G6" s="86" t="e">
+      <c r="G6" s="88" t="e">
         <f>_xlfn.XLOOKUP(J6,$A$2:$A$6,#REF!,"N/A",0)</f>
         <v>#NUM!</v>
       </c>
-      <c r="H6" s="87"/>
-      <c r="I6" s="87"/>
-      <c r="J6" s="87" t="e">
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="89" t="e">
         <f>LARGE($A$2:$A$6,3)</f>
         <v>#NUM!</v>
       </c>
-      <c r="K6" s="87"/>
+      <c r="K6" s="89"/>
       <c r="L6" s="58" t="str">
         <f>IFERROR(((J6*100)/#REF!),"N/A")</f>
         <v>N/A</v>
@@ -68472,26 +68357,26 @@
       <c r="A9" s="5" t="s">
         <v>545</v>
       </c>
-      <c r="B9" s="95" t="s">
+      <c r="B9" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="96"/>
-      <c r="D9" s="95" t="s">
+      <c r="C9" s="78"/>
+      <c r="D9" s="77" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="96"/>
+      <c r="E9" s="78"/>
       <c r="F9" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="95" t="s">
+      <c r="G9" s="77" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="97"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="95" t="s">
+      <c r="H9" s="84"/>
+      <c r="I9" s="78"/>
+      <c r="J9" s="77" t="s">
         <v>47</v>
       </c>
-      <c r="K9" s="96"/>
+      <c r="K9" s="78"/>
       <c r="L9" s="59" t="s">
         <v>48</v>
       </c>
@@ -68500,42 +68385,42 @@
       <c r="A10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="88" t="s">
+      <c r="B10" s="73" t="s">
         <v>551</v>
       </c>
-      <c r="C10" s="89"/>
-      <c r="D10" s="89"/>
-      <c r="E10" s="89"/>
-      <c r="F10" s="89"/>
-      <c r="G10" s="89"/>
-      <c r="H10" s="89"/>
-      <c r="I10" s="89"/>
-      <c r="J10" s="89"/>
-      <c r="K10" s="89"/>
-      <c r="L10" s="89"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="74"/>
+      <c r="J10" s="74"/>
+      <c r="K10" s="74"/>
+      <c r="L10" s="74"/>
     </row>
     <row r="11" spans="1:12" ht="18" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="79" t="s">
+      <c r="B11" s="82" t="s">
         <v>552</v>
       </c>
-      <c r="C11" s="79"/>
-      <c r="D11" s="80" t="s">
+      <c r="C11" s="82"/>
+      <c r="D11" s="83" t="s">
         <v>553</v>
       </c>
-      <c r="E11" s="80"/>
+      <c r="E11" s="83"/>
       <c r="F11" s="54"/>
-      <c r="G11" s="90" t="s">
+      <c r="G11" s="79" t="s">
         <v>554</v>
       </c>
-      <c r="H11" s="91"/>
-      <c r="I11" s="92"/>
-      <c r="J11" s="93" t="s">
+      <c r="H11" s="80"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="75" t="s">
         <v>556</v>
       </c>
-      <c r="K11" s="94"/>
+      <c r="K11" s="76"/>
       <c r="L11" s="55" t="s">
         <v>557</v>
       </c>
@@ -68544,26 +68429,26 @@
       <c r="A12" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="79" t="s">
+      <c r="B12" s="82" t="s">
         <v>558</v>
       </c>
-      <c r="C12" s="79"/>
-      <c r="D12" s="80" t="s">
+      <c r="C12" s="82"/>
+      <c r="D12" s="83" t="s">
         <v>559</v>
       </c>
-      <c r="E12" s="80"/>
+      <c r="E12" s="83"/>
       <c r="F12" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="G12" s="81" t="s">
+      <c r="G12" s="90" t="s">
         <v>561</v>
       </c>
-      <c r="H12" s="82"/>
-      <c r="I12" s="82"/>
-      <c r="J12" s="82" t="s">
+      <c r="H12" s="91"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="91" t="s">
         <v>562</v>
       </c>
-      <c r="K12" s="82"/>
+      <c r="K12" s="91"/>
       <c r="L12" s="57" t="s">
         <v>563</v>
       </c>
@@ -68572,26 +68457,26 @@
       <c r="A13" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="79" t="s">
+      <c r="B13" s="82" t="s">
         <v>564</v>
       </c>
-      <c r="C13" s="79"/>
-      <c r="D13" s="83" t="s">
+      <c r="C13" s="82"/>
+      <c r="D13" s="92" t="s">
         <v>565</v>
       </c>
-      <c r="E13" s="83"/>
+      <c r="E13" s="92"/>
       <c r="F13" s="56" t="s">
         <v>566</v>
       </c>
-      <c r="G13" s="84" t="s">
+      <c r="G13" s="85" t="s">
         <v>567</v>
       </c>
-      <c r="H13" s="85"/>
-      <c r="I13" s="85"/>
-      <c r="J13" s="85" t="s">
+      <c r="H13" s="86"/>
+      <c r="I13" s="86"/>
+      <c r="J13" s="86" t="s">
         <v>568</v>
       </c>
-      <c r="K13" s="85"/>
+      <c r="K13" s="86"/>
       <c r="L13" s="57" t="s">
         <v>569</v>
       </c>
@@ -68600,38 +68485,43 @@
       <c r="A14" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="79"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="83"/>
-      <c r="E14" s="83"/>
+      <c r="B14" s="82"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="92"/>
       <c r="F14" s="56" t="s">
         <v>570</v>
       </c>
-      <c r="G14" s="86" t="s">
+      <c r="G14" s="88" t="s">
         <v>571</v>
       </c>
-      <c r="H14" s="87"/>
-      <c r="I14" s="87"/>
-      <c r="J14" s="87" t="s">
+      <c r="H14" s="89"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="89" t="s">
         <v>572</v>
       </c>
-      <c r="K14" s="87"/>
+      <c r="K14" s="89"/>
       <c r="L14" s="58" t="s">
         <v>573</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="B13:C14"/>
+    <mergeCell ref="D13:E14"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="B10:L10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:K11"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="G9:I9"/>
@@ -68646,48 +68536,43 @@
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="J4:K4"/>
-    <mergeCell ref="B10:L10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="B13:C14"/>
-    <mergeCell ref="D13:E14"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="B1:C1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="D5">
-    <cfRule type="cellIs" dxfId="7" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="15" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="16" operator="equal">
       <formula>86.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="17" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="17" operator="lessThan">
       <formula>86.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="18" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="18" operator="greaterThan">
       <formula>86.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>86.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
       <formula>86.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="greaterThan">
       <formula>86.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68896,14 +68781,14 @@
         <v>41</v>
       </c>
       <c r="B2" s="14"/>
-      <c r="C2" s="101" t="s">
+      <c r="C2" s="93" t="s">
         <v>404</v>
       </c>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
       <c r="I2" s="17"/>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69017,14 +68902,14 @@
         <v>41</v>
       </c>
       <c r="B9" s="14"/>
-      <c r="C9" s="101" t="s">
+      <c r="C9" s="93" t="s">
         <v>387</v>
       </c>
-      <c r="D9" s="101"/>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="101"/>
-      <c r="H9" s="101"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
       <c r="I9" s="17"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -69176,7 +69061,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D077AAEA-2C62-4252-81FA-F27EE73ED170}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="37.28515625" customWidth="1"/>
@@ -69230,18 +69115,18 @@
       <c r="A2" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
     </row>
     <row r="3" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A3" s="9" t="s">
@@ -69397,26 +69282,18 @@
       <c r="A9" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="K9" s="11"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
     </row>
     <row r="10" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A10" s="9" t="s">
@@ -69425,373 +69302,321 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="70" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="1:11" ht="24" x14ac:dyDescent="0.4">
-      <c r="A11" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="68"/>
-      <c r="H11" s="68"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>52</v>
-      </c>
+    <row r="14" spans="1:11" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="61" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="61"/>
     </row>
-    <row r="15" spans="1:11" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A15" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="69" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="69"/>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="69"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="69"/>
-      <c r="J15" s="69"/>
-      <c r="K15" s="69"/>
+        <v>53</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A16" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A17" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A18" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A19" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A20" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>104</v>
+        <v>164</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>110</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A21" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="K21" s="11" t="s">
-        <v>167</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="62" t="s">
+        <v>130</v>
+      </c>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
     </row>
     <row r="22" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A22" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>586</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>588</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>590</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>592</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="K22" s="11" t="s">
-        <v>593</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="60" t="s">
+        <v>168</v>
+      </c>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
     </row>
-    <row r="23" spans="1:11" ht="24" x14ac:dyDescent="0.4">
-      <c r="A23" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="70" t="s">
-        <v>130</v>
-      </c>
-      <c r="F23" s="70"/>
-      <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-    </row>
-    <row r="24" spans="1:11" ht="24" x14ac:dyDescent="0.4">
-      <c r="A24" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="68" t="s">
-        <v>168</v>
-      </c>
-      <c r="F24" s="68"/>
-      <c r="G24" s="68"/>
-      <c r="H24" s="68"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E25" s="16"/>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E23" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E22:H22"/>
     <mergeCell ref="B2:K2"/>
+    <mergeCell ref="E9:H9"/>
     <mergeCell ref="E10:H10"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="B15:K15"/>
-    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="B14:K14"/>
+    <mergeCell ref="E21:H21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -71574,47 +71399,47 @@
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E9" s="73" t="s">
+      <c r="E9" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73" t="s">
+      <c r="F9" s="65"/>
+      <c r="G9" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="73"/>
+      <c r="H9" s="65"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D10" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="74" t="s">
+      <c r="E10" s="66" t="s">
         <v>546</v>
       </c>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="K10" s="61" t="s">
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="K10" s="95" t="s">
         <v>574</v>
       </c>
-      <c r="L10" s="62" t="s">
+      <c r="L10" s="96" t="s">
         <v>575</v>
       </c>
-      <c r="M10" s="62" t="s">
+      <c r="M10" s="96" t="s">
         <v>7</v>
       </c>
-      <c r="N10" s="62" t="s">
+      <c r="N10" s="96" t="s">
         <v>441</v>
       </c>
-      <c r="O10" s="62" t="s">
+      <c r="O10" s="96" t="s">
         <v>440</v>
       </c>
-      <c r="P10" s="62" t="s">
+      <c r="P10" s="96" t="s">
         <v>577</v>
       </c>
-      <c r="Q10" s="62" t="s">
+      <c r="Q10" s="96" t="s">
         <v>576</v>
       </c>
-      <c r="R10" s="63" t="s">
+      <c r="R10" s="97" t="s">
         <v>578</v>
       </c>
     </row>
@@ -71622,110 +71447,110 @@
       <c r="D11" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="75" t="s">
+      <c r="E11" s="67" t="s">
         <v>547</v>
       </c>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="K11" s="64"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="K11" s="98"/>
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" s="17"/>
       <c r="O11" s="17"/>
       <c r="P11" s="17"/>
       <c r="Q11" s="17"/>
-      <c r="R11" s="65"/>
+      <c r="R11" s="99"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D12" s="71" t="s">
+      <c r="D12" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="76" t="s">
+      <c r="E12" s="68" t="s">
         <v>548</v>
       </c>
-      <c r="F12" s="76"/>
-      <c r="G12" s="77" t="s">
+      <c r="F12" s="68"/>
+      <c r="G12" s="69" t="s">
         <v>549</v>
       </c>
-      <c r="H12" s="77"/>
-      <c r="K12" s="66"/>
-      <c r="L12" s="67"/>
-      <c r="M12" s="67"/>
-      <c r="N12" s="67"/>
-      <c r="O12" s="67"/>
-      <c r="P12" s="67"/>
-      <c r="Q12" s="67"/>
-      <c r="R12" s="60"/>
+      <c r="H12" s="69"/>
+      <c r="K12" s="100"/>
+      <c r="L12" s="101"/>
+      <c r="M12" s="101"/>
+      <c r="N12" s="101"/>
+      <c r="O12" s="101"/>
+      <c r="P12" s="101"/>
+      <c r="Q12" s="101"/>
+      <c r="R12" s="94"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D13" s="72"/>
-      <c r="E13" s="76"/>
-      <c r="F13" s="76"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="K13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+      <c r="K13" s="98"/>
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" s="17"/>
       <c r="O13" s="17"/>
       <c r="P13" s="17"/>
       <c r="Q13" s="17"/>
-      <c r="R13" s="65"/>
+      <c r="R13" s="99"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D14" s="72"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="76"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
-      <c r="K14" s="66"/>
-      <c r="L14" s="67"/>
-      <c r="M14" s="67"/>
-      <c r="N14" s="67"/>
-      <c r="O14" s="67"/>
-      <c r="P14" s="67"/>
-      <c r="Q14" s="67"/>
-      <c r="R14" s="60"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="K14" s="100"/>
+      <c r="L14" s="101"/>
+      <c r="M14" s="101"/>
+      <c r="N14" s="101"/>
+      <c r="O14" s="101"/>
+      <c r="P14" s="101"/>
+      <c r="Q14" s="101"/>
+      <c r="R14" s="94"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D15" s="72"/>
-      <c r="E15" s="76"/>
-      <c r="F15" s="76"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="77"/>
+      <c r="D15" s="64"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D16" s="71" t="s">
+      <c r="D16" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="76"/>
-      <c r="F16" s="76"/>
-      <c r="G16" s="78" t="s">
+      <c r="E16" s="68"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="70" t="s">
         <v>550</v>
       </c>
-      <c r="H16" s="78"/>
+      <c r="H16" s="70"/>
     </row>
     <row r="17" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D17" s="72"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="76"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70"/>
     </row>
     <row r="18" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D18" s="72"/>
-      <c r="E18" s="76"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="78"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
     </row>
     <row r="19" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D19" s="72"/>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="78"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -71927,7 +71752,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E87CC77D-451D-4938-839F-1695B8C726C1}">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -72508,96 +72333,6 @@
       </c>
       <c r="H32" s="3" t="s">
         <v>544</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="102" t="s">
-        <v>594</v>
-      </c>
-      <c r="B33" s="102" t="s">
-        <v>595</v>
-      </c>
-      <c r="C33" s="103"/>
-      <c r="F33" s="102" t="s">
-        <v>594</v>
-      </c>
-      <c r="G33" s="102" t="s">
-        <v>604</v>
-      </c>
-      <c r="H33" s="103" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>596</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>597</v>
-      </c>
-      <c r="C34" s="3"/>
-      <c r="F34" s="4" t="s">
-        <v>596</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>605</v>
-      </c>
-      <c r="H34" s="103" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>598</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>599</v>
-      </c>
-      <c r="C35" s="3"/>
-      <c r="F35" s="4" t="s">
-        <v>598</v>
-      </c>
-      <c r="G35" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="H35" s="103" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>600</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>601</v>
-      </c>
-      <c r="C36" s="3"/>
-      <c r="F36" s="4" t="s">
-        <v>600</v>
-      </c>
-      <c r="G36" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="H36" s="103" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>602</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>603</v>
-      </c>
-      <c r="C37" s="3"/>
-      <c r="F37" s="4" t="s">
-        <v>602</v>
-      </c>
-      <c r="G37" s="14" t="s">
-        <v>608</v>
-      </c>
-      <c r="H37" s="103" t="s">
-        <v>613</v>
       </c>
     </row>
   </sheetData>
